--- a/data/trans_orig/P04D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30729</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55306</t>
+          <t>55571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41016</t>
+          <t>42781</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69415</t>
+          <t>69441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80227</t>
+          <t>80818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116527</t>
+          <t>118675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157105</t>
+          <t>157291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191957</t>
+          <t>191992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140842</t>
+          <t>140980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176159</t>
+          <t>177060</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>309256</t>
+          <t>305278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356271</t>
+          <t>357014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61879</t>
+          <t>63037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92938</t>
+          <t>95366</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59226</t>
+          <t>60403</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90214</t>
+          <t>88729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>131860</t>
+          <t>129522</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>175186</t>
+          <t>174859</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55434</t>
+          <t>57164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59502</t>
+          <t>61087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>69916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105491</t>
+          <t>107272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>320965</t>
+          <t>317717</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>363138</t>
+          <t>361724</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>340410</t>
+          <t>339344</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>384365</t>
+          <t>384245</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>675276</t>
+          <t>674298</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>736797</t>
+          <t>737236</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102682</t>
+          <t>103893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142037</t>
+          <t>145167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97727</t>
+          <t>97808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137324</t>
+          <t>136232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209904</t>
+          <t>209657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>265710</t>
+          <t>267873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>228099</t>
+          <t>227667</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>258865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252747</t>
+          <t>254130</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>284296</t>
+          <t>283936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>491635</t>
+          <t>492614</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>534679</t>
+          <t>534438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62359</t>
+          <t>62166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92984</t>
+          <t>92667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54068</t>
+          <t>54571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>84157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124278</t>
+          <t>125293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166384</t>
+          <t>166164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20101</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>18550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32920</t>
+          <t>33114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198383</t>
+          <t>198747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>239295</t>
+          <t>237455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>222384</t>
+          <t>221733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>261954</t>
+          <t>261249</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433220</t>
+          <t>428784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>491013</t>
+          <t>485639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124750</t>
+          <t>125591</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>164337</t>
+          <t>163983</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117912</t>
+          <t>117383</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>156414</t>
+          <t>155457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>251496</t>
+          <t>256942</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>309254</t>
+          <t>312745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>17679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>20490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32657</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>116285</t>
+          <t>115527</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>146310</t>
+          <t>145808</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102556</t>
+          <t>100521</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>131373</t>
+          <t>131141</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>225840</t>
+          <t>226520</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>268938</t>
+          <t>269853</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,44%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57485</t>
+          <t>58467</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85944</t>
+          <t>87867</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76268</t>
+          <t>76646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105290</t>
+          <t>106488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141592</t>
+          <t>141019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183558</t>
+          <t>183402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>172307</t>
+          <t>171632</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204289</t>
+          <t>203756</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>184011</t>
+          <t>185742</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>215079</t>
+          <t>215271</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>365024</t>
+          <t>366720</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>411697</t>
+          <t>411600</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,29%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68255</t>
+          <t>68384</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>100415</t>
+          <t>100468</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63546</t>
+          <t>63048</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94810</t>
+          <t>91694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>138697</t>
+          <t>138466</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>184400</t>
+          <t>183416</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,82 +3483,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>17354</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>27060</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>29038</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>19185</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>41516</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>3,06%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>17354</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>10577</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>28512</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>29038</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>18072</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>40457</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>458600</t>
+          <t>457031</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>506731</t>
+          <t>507543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>477719</t>
+          <t>477935</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>527560</t>
+          <t>526223</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>950780</t>
+          <t>952588</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1021522</t>
+          <t>1020422</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>147203</t>
+          <t>145563</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>194204</t>
+          <t>193790</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>149329</t>
+          <t>150243</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>198500</t>
+          <t>195920</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>308178</t>
+          <t>307075</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>375082</t>
+          <t>372262</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32515</t>
+          <t>33213</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25767</t>
+          <t>26262</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51564</t>
+          <t>51386</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>340917</t>
+          <t>342919</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>398370</t>
+          <t>399974</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>413651</t>
+          <t>412980</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>474116</t>
+          <t>473408</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>776233</t>
+          <t>772438</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>860161</t>
+          <t>856925</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>358144</t>
+          <t>356698</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>413731</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>336361</t>
+          <t>338596</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>395410</t>
+          <t>396020</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>706832</t>
+          <t>707840</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>789625</t>
+          <t>791252</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>120094</t>
+          <t>118571</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>167483</t>
+          <t>167116</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>135657</t>
+          <t>136385</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>186311</t>
+          <t>187873</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>270685</t>
+          <t>267675</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>341272</t>
+          <t>337458</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2098435</t>
+          <t>2100521</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2215012</t>
+          <t>2219218</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2233409</t>
+          <t>2238353</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2351145</t>
+          <t>2357039</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4361926</t>
+          <t>4364789</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4531813</t>
+          <t>4534816</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1070530</t>
+          <t>1072620</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1186341</t>
+          <t>1184169</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1046238</t>
+          <t>1045111</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1158167</t>
+          <t>1160957</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2152638</t>
+          <t>2142505</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2315069</t>
+          <t>2305997</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125834</t>
+          <t>127434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>164036</t>
+          <t>162962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110902</t>
+          <t>112301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144513</t>
+          <t>145899</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249999</t>
+          <t>250892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299368</t>
+          <t>299411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32766</t>
+          <t>33104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58156</t>
+          <t>58490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31014</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55913</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70358</t>
+          <t>69953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105548</t>
+          <t>105272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86419</t>
+          <t>85192</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121542</t>
+          <t>118287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102412</t>
+          <t>101893</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137008</t>
+          <t>134411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>195681</t>
+          <t>199024</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>245417</t>
+          <t>244365</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,95%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>116879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158070</t>
+          <t>156324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100627</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140486</t>
+          <t>139940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228066</t>
+          <t>229487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>285966</t>
+          <t>284834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153416</t>
+          <t>155265</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>197522</t>
+          <t>198558</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>146522</t>
+          <t>146809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>191040</t>
+          <t>192214</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>314787</t>
+          <t>315637</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>377029</t>
+          <t>376809</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168235</t>
+          <t>169741</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214547</t>
+          <t>212156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209458</t>
+          <t>210613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256935</t>
+          <t>257056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391751</t>
+          <t>391841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>458525</t>
+          <t>457971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>240744</t>
+          <t>240632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268318</t>
+          <t>268231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>257077</t>
+          <t>256789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>286021</t>
+          <t>284956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>509010</t>
+          <t>505801</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>547995</t>
+          <t>546550</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>44397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71516</t>
+          <t>71422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48112</t>
+          <t>48212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76100</t>
+          <t>76020</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99105</t>
+          <t>99748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137707</t>
+          <t>138614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>49334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210648</t>
+          <t>209111</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>247077</t>
+          <t>247023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>222135</t>
+          <t>222278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>261303</t>
+          <t>263270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>443904</t>
+          <t>440122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>500458</t>
+          <t>497251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110095</t>
+          <t>108719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>145351</t>
+          <t>145490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106878</t>
+          <t>105976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146884</t>
+          <t>145956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>223934</t>
+          <t>227461</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281185</t>
+          <t>281307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>178673</t>
+          <t>179520</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196962</t>
+          <t>196838</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>183913</t>
+          <t>183882</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>201959</t>
+          <t>201386</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>369652</t>
+          <t>368785</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>395346</t>
+          <t>393768</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29284</t>
+          <t>28232</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27722</t>
+          <t>28900</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51515</t>
+          <t>51586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76123</t>
+          <t>77758</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>107524</t>
+          <t>108592</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79025</t>
+          <t>78791</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>111497</t>
+          <t>109750</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>163988</t>
+          <t>162893</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>207409</t>
+          <t>209508</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52640</t>
+          <t>53426</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81343</t>
+          <t>82166</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52265</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80772</t>
+          <t>79207</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111769</t>
+          <t>112543</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150955</t>
+          <t>152575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90573</t>
+          <t>91448</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>122164</t>
+          <t>122563</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95962</t>
+          <t>97829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>129510</t>
+          <t>132313</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>198202</t>
+          <t>197943</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>243226</t>
+          <t>244547</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>110782</t>
+          <t>110703</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>152325</t>
+          <t>155464</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116336</t>
+          <t>115490</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>159569</t>
+          <t>161868</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>240423</t>
+          <t>240568</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>304923</t>
+          <t>300333</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>309800</t>
+          <t>306477</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>363914</t>
+          <t>364795</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>326853</t>
+          <t>324796</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>380478</t>
+          <t>378921</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>650518</t>
+          <t>650649</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>727973</t>
+          <t>727041</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>165645</t>
+          <t>163416</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>212307</t>
+          <t>213242</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>177930</t>
+          <t>177404</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>229481</t>
+          <t>229845</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>353692</t>
+          <t>357174</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>422852</t>
+          <t>427728</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>23749</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>470049</t>
+          <t>471443</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>526599</t>
+          <t>526205</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>479604</t>
+          <t>479241</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>537664</t>
+          <t>537451</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>970792</t>
+          <t>970167</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1048773</t>
+          <t>1049988</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>247249</t>
+          <t>247656</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>303064</t>
+          <t>302939</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>278754</t>
+          <t>280315</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>337149</t>
+          <t>338528</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>544734</t>
+          <t>543272</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>620985</t>
+          <t>622077</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>488903</t>
+          <t>492038</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>580562</t>
+          <t>577072</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>473334</t>
+          <t>476803</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>561205</t>
+          <t>562513</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>984256</t>
+          <t>986040</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1108322</t>
+          <t>1118529</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1732432</t>
+          <t>1738456</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1852822</t>
+          <t>1856736</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1789213</t>
+          <t>1781384</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1905217</t>
+          <t>1905651</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3557527</t>
+          <t>3560251</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3718251</t>
+          <t>3726090</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1006469</t>
+          <t>1013439</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1119401</t>
+          <t>1120759</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1124450</t>
+          <t>1124295</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1241712</t>
+          <t>1239099</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2164138</t>
+          <t>2170944</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2329712</t>
+          <t>2326782</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41760</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77618</t>
+          <t>77547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43407</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69672</t>
+          <t>67128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92007</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134939</t>
+          <t>133184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110361</t>
+          <t>111680</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153063</t>
+          <t>155115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122851</t>
+          <t>123353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152435</t>
+          <t>151700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244605</t>
+          <t>244462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>295905</t>
+          <t>295536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103857</t>
+          <t>104482</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146547</t>
+          <t>145488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85381</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112586</t>
+          <t>111479</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>196681</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>247991</t>
+          <t>246253</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40595</t>
+          <t>40053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78546</t>
+          <t>75469</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>45714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70082</t>
+          <t>69841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93685</t>
+          <t>94371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138316</t>
+          <t>137696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>410781</t>
+          <t>411588</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>454439</t>
+          <t>453364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>421863</t>
+          <t>422922</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>450096</t>
+          <t>450185</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>841426</t>
+          <t>846888</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>895814</t>
+          <t>896981</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43180</t>
+          <t>44170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30477</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>34635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>67578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28435</t>
+          <t>28092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210570</t>
+          <t>210731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242963</t>
+          <t>242573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>241935</t>
+          <t>241345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>269827</t>
+          <t>270284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>459921</t>
+          <t>459453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>503176</t>
+          <t>502680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62141</t>
+          <t>62337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93842</t>
+          <t>93312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71681</t>
+          <t>71667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99520</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142232</t>
+          <t>143068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184489</t>
+          <t>182977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231271</t>
+          <t>241992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28723</t>
+          <t>29481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298810</t>
+          <t>285142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98047</t>
+          <t>100450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139636</t>
+          <t>143024</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>133162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>264290</t>
+          <t>266890</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245562</t>
+          <t>248568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392742</t>
+          <t>391795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161583</t>
+          <t>158256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>203339</t>
+          <t>201741</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110771</t>
+          <t>111583</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220484</t>
+          <t>225771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>262742</t>
+          <t>257949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>416249</t>
+          <t>409791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>173899</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>178352</t>
+          <t>178417</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>245961</t>
+          <t>245537</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>255550</t>
+          <t>255585</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>422276</t>
+          <t>422142</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>432576</t>
+          <t>432886</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131521</t>
+          <t>131748</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>161576</t>
+          <t>161225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>124570</t>
+          <t>124588</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150678</t>
+          <t>150808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>265283</t>
+          <t>263155</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>303455</t>
+          <t>303499</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103680</t>
+          <t>102909</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133906</t>
+          <t>133626</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101216</t>
+          <t>100995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>127420</t>
+          <t>127399</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>212240</t>
+          <t>213275</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>251480</t>
+          <t>253175</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>175162</t>
+          <t>175241</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>232030</t>
+          <t>228634</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116932</t>
+          <t>107493</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>291404</t>
+          <t>291296</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>265645</t>
+          <t>268562</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>498367</t>
+          <t>498272</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>174467</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>230047</t>
+          <t>231385</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>243829</t>
+          <t>242686</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>597951</t>
+          <t>626924</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>443176</t>
+          <t>444491</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>944081</t>
+          <t>905663</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>61,46%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>196243</t>
+          <t>194609</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>250070</t>
+          <t>249713</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>123368</t>
+          <t>111645</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>322247</t>
+          <t>322401</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>276360</t>
+          <t>294514</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>545948</t>
+          <t>547133</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>27242</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>48229</t>
+          <t>49470</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>277846</t>
+          <t>274083</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>848629</t>
+          <t>848763</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>636601</t>
+          <t>636660</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>662030</t>
+          <t>662432</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>793485</t>
+          <t>792469</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1499452</t>
+          <t>1499292</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>56879</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>642957</t>
+          <t>645064</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>39545</t>
+          <t>39139</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>61581</t>
+          <t>62232</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>106711</t>
+          <t>107403</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>832211</t>
+          <t>826550</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,2%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>284567</t>
+          <t>276593</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>410684</t>
+          <t>411854</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>360218</t>
+          <t>358228</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>665407</t>
+          <t>630368</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>697379</t>
+          <t>697165</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1047950</t>
+          <t>1008827</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1534447</t>
+          <t>1564751</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2234853</t>
+          <t>2234341</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2344843</t>
+          <t>2339506</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2697045</t>
+          <t>2684967</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4006382</t>
+          <t>4000677</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4768861</t>
+          <t>4785092</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>840456</t>
+          <t>836418</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1655221</t>
+          <t>1618815</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>636803</t>
+          <t>629149</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>859315</t>
+          <t>861343</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1605976</t>
+          <t>1589681</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2581119</t>
+          <t>2486275</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55571</t>
+          <t>54981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42781</t>
+          <t>42689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69441</t>
+          <t>69759</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80818</t>
+          <t>79317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118675</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157291</t>
+          <t>158192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191992</t>
+          <t>192333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140980</t>
+          <t>139669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>177060</t>
+          <t>175393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305278</t>
+          <t>309374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>357014</t>
+          <t>358590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63037</t>
+          <t>63201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95366</t>
+          <t>92450</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60403</t>
+          <t>59395</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>88729</t>
+          <t>89573</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>129522</t>
+          <t>131313</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>174859</t>
+          <t>173731</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57164</t>
+          <t>53880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>31939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>59817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69916</t>
+          <t>68428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107272</t>
+          <t>107213</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>317717</t>
+          <t>319740</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>361724</t>
+          <t>364464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>339344</t>
+          <t>340818</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>384245</t>
+          <t>382389</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>674298</t>
+          <t>670799</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>737236</t>
+          <t>734168</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103893</t>
+          <t>102580</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145167</t>
+          <t>141310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97808</t>
+          <t>99498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136232</t>
+          <t>136433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209657</t>
+          <t>212587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>267873</t>
+          <t>265767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>227667</t>
+          <t>228613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258865</t>
+          <t>258982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>254130</t>
+          <t>252805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>283936</t>
+          <t>283547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>492614</t>
+          <t>489722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>534438</t>
+          <t>533415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,2%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62166</t>
+          <t>61694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92667</t>
+          <t>92746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54571</t>
+          <t>54661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84157</t>
+          <t>85036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125293</t>
+          <t>126130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166164</t>
+          <t>168688</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>21797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18550</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>33902</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198747</t>
+          <t>196836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237455</t>
+          <t>237411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>221733</t>
+          <t>221279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>261249</t>
+          <t>259802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>428784</t>
+          <t>432613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>485639</t>
+          <t>487722</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125591</t>
+          <t>126479</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163983</t>
+          <t>164857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117383</t>
+          <t>118903</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155457</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>256942</t>
+          <t>255216</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>312745</t>
+          <t>308245</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14154</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32562</t>
+          <t>33360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>115527</t>
+          <t>117687</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>145808</t>
+          <t>146844</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100521</t>
+          <t>102479</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>131141</t>
+          <t>131190</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>226520</t>
+          <t>226986</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>269853</t>
+          <t>268111</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,03%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58467</t>
+          <t>57849</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87867</t>
+          <t>85546</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76646</t>
+          <t>77485</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106488</t>
+          <t>105146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141019</t>
+          <t>142606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183402</t>
+          <t>182892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>171632</t>
+          <t>171317</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>203756</t>
+          <t>202113</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>185742</t>
+          <t>183471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>215271</t>
+          <t>215288</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>366720</t>
+          <t>366484</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>411600</t>
+          <t>410051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68384</t>
+          <t>69494</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>100468</t>
+          <t>100744</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63048</t>
+          <t>62779</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91694</t>
+          <t>93909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>138466</t>
+          <t>139617</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>183416</t>
+          <t>184721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10077</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>27783</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,47 +3518,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>29038</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>19697</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>42530</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>29038</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>19185</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>41516</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>457031</t>
+          <t>458806</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>507543</t>
+          <t>506640</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>477935</t>
+          <t>480384</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>526223</t>
+          <t>528311</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>952588</t>
+          <t>954205</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1020422</t>
+          <t>1020272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>145563</t>
+          <t>145763</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>193790</t>
+          <t>191205</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>150243</t>
+          <t>149362</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>195920</t>
+          <t>195763</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>307075</t>
+          <t>306925</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>372262</t>
+          <t>373660</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>15048</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33213</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23457</t>
+          <t>23886</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26262</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51386</t>
+          <t>50695</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>342919</t>
+          <t>339863</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>399974</t>
+          <t>399803</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>412980</t>
+          <t>414249</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>473408</t>
+          <t>473750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>772438</t>
+          <t>772495</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>856925</t>
+          <t>857405</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,49%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>356698</t>
+          <t>355549</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>413731</t>
+          <t>415336</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>338596</t>
+          <t>336632</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>396020</t>
+          <t>395963</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>707840</t>
+          <t>707215</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>791252</t>
+          <t>792818</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>118571</t>
+          <t>117106</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>167116</t>
+          <t>167635</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>136385</t>
+          <t>136262</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>187873</t>
+          <t>189018</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>267675</t>
+          <t>269652</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>337458</t>
+          <t>339063</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2100521</t>
+          <t>2096764</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2219218</t>
+          <t>2214659</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2238353</t>
+          <t>2238515</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2357039</t>
+          <t>2352332</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4364789</t>
+          <t>4362800</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4534816</t>
+          <t>4534267</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1072620</t>
+          <t>1076408</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1184169</t>
+          <t>1189026</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1045111</t>
+          <t>1047579</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1160957</t>
+          <t>1153325</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2142505</t>
+          <t>2148760</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2305997</t>
+          <t>2308780</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127434</t>
+          <t>129014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162962</t>
+          <t>164654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112301</t>
+          <t>110585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145899</t>
+          <t>145804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>250892</t>
+          <t>248475</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299411</t>
+          <t>299129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33104</t>
+          <t>34316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58490</t>
+          <t>59780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55090</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69953</t>
+          <t>69715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105272</t>
+          <t>105670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85192</t>
+          <t>85703</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118287</t>
+          <t>119973</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101893</t>
+          <t>102574</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134411</t>
+          <t>136018</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>199024</t>
+          <t>197707</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>244365</t>
+          <t>246034</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116879</t>
+          <t>115934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156324</t>
+          <t>155731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101698</t>
+          <t>101903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139940</t>
+          <t>142481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229487</t>
+          <t>226234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284834</t>
+          <t>284554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155265</t>
+          <t>157484</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198558</t>
+          <t>197881</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>146809</t>
+          <t>149156</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>192214</t>
+          <t>190342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>315637</t>
+          <t>312217</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>376809</t>
+          <t>374705</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169741</t>
+          <t>168340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212156</t>
+          <t>213030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210613</t>
+          <t>209279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>257571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391841</t>
+          <t>393109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>457971</t>
+          <t>457731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>897</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>240632</t>
+          <t>241284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268231</t>
+          <t>269259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>256789</t>
+          <t>257969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>284956</t>
+          <t>285835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>505801</t>
+          <t>508150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>546550</t>
+          <t>549089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>44383</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71422</t>
+          <t>70881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48212</t>
+          <t>47490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76020</t>
+          <t>74903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99748</t>
+          <t>97693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138614</t>
+          <t>137202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29391</t>
+          <t>29824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>23305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49334</t>
+          <t>46610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209111</t>
+          <t>207633</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>247023</t>
+          <t>245826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>222278</t>
+          <t>222528</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>263270</t>
+          <t>261602</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>440122</t>
+          <t>442974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>497251</t>
+          <t>496999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108719</t>
+          <t>108801</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>145490</t>
+          <t>146590</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>105976</t>
+          <t>107802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145956</t>
+          <t>145953</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>227461</t>
+          <t>227486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281307</t>
+          <t>281355</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>179520</t>
+          <t>178905</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196838</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>183882</t>
+          <t>184296</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>201386</t>
+          <t>201501</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>368785</t>
+          <t>369328</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>393768</t>
+          <t>395785</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28232</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28900</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51586</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77758</t>
+          <t>75539</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108592</t>
+          <t>104992</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78791</t>
+          <t>78709</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109750</t>
+          <t>109913</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>162893</t>
+          <t>162512</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>209508</t>
+          <t>207627</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>82166</t>
+          <t>81713</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>51767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79207</t>
+          <t>80424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112543</t>
+          <t>111064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>152575</t>
+          <t>151160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>91448</t>
+          <t>89938</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>122563</t>
+          <t>122362</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>97829</t>
+          <t>96721</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>132313</t>
+          <t>129644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>197943</t>
+          <t>197946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>244547</t>
+          <t>243672</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>110703</t>
+          <t>113238</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>155464</t>
+          <t>158607</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>115490</t>
+          <t>116248</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161868</t>
+          <t>160433</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>240568</t>
+          <t>240387</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>300333</t>
+          <t>301698</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>306477</t>
+          <t>309542</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>364795</t>
+          <t>365185</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>324796</t>
+          <t>324048</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>378921</t>
+          <t>379912</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>650649</t>
+          <t>648948</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>727041</t>
+          <t>722536</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>163416</t>
+          <t>162068</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>213242</t>
+          <t>212083</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>177404</t>
+          <t>177960</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>229845</t>
+          <t>228339</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>357174</t>
+          <t>355947</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>427728</t>
+          <t>426903</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23749</t>
+          <t>23279</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>471443</t>
+          <t>469187</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>526205</t>
+          <t>525626</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>479241</t>
+          <t>478362</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>537451</t>
+          <t>535260</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>970167</t>
+          <t>969475</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1049988</t>
+          <t>1050285</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>247656</t>
+          <t>246909</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>302939</t>
+          <t>303635</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>280315</t>
+          <t>281961</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>338528</t>
+          <t>338455</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>543272</t>
+          <t>541352</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>622077</t>
+          <t>621006</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>492038</t>
+          <t>491481</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>577072</t>
+          <t>577793</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>476803</t>
+          <t>472346</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>562513</t>
+          <t>560787</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>986040</t>
+          <t>995617</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1118529</t>
+          <t>1107542</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1738456</t>
+          <t>1739624</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1856736</t>
+          <t>1855218</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1781384</t>
+          <t>1785061</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1905651</t>
+          <t>1908236</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3560251</t>
+          <t>3556327</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3726090</t>
+          <t>3722595</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1013439</t>
+          <t>1012908</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1120759</t>
+          <t>1122201</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1124295</t>
+          <t>1128057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1239099</t>
+          <t>1244241</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2170944</t>
+          <t>2164920</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2326782</t>
+          <t>2328753</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -9407,32 +9407,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>56858</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77547</t>
+          <t>95759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>52757</t>
+          <t>68293</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>57757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67128</t>
+          <t>82590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9477,32 +9477,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>109614</t>
+          <t>146671</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90161</t>
+          <t>128780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133184</t>
+          <t>169340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -9520,32 +9520,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>131516</t>
+          <t>124748</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111680</t>
+          <t>108059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155115</t>
+          <t>143675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9555,32 +9555,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>137481</t>
+          <t>143956</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123353</t>
+          <t>128904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151700</t>
+          <t>158933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9590,32 +9590,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>268996</t>
+          <t>268704</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244462</t>
+          <t>246059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>295536</t>
+          <t>292122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -9633,32 +9633,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123069</t>
+          <t>115719</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104482</t>
+          <t>98366</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>145488</t>
+          <t>133681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9668,32 +9668,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99398</t>
+          <t>103812</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86038</t>
+          <t>91289</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>118672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9703,32 +9703,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>222467</t>
+          <t>219531</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>197102</t>
+          <t>196868</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>246253</t>
+          <t>243209</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -9746,17 +9746,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9816,17 +9816,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>58667</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40053</t>
+          <t>42343</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75469</t>
+          <t>79018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9898,32 +9898,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>56546</t>
+          <t>56708</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45714</t>
+          <t>44953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69841</t>
+          <t>68816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9933,32 +9933,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>113722</t>
+          <t>115375</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94371</t>
+          <t>98114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137696</t>
+          <t>144868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -9976,32 +9976,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>434523</t>
+          <t>443839</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>411588</t>
+          <t>419984</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>453364</t>
+          <t>463309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10011,32 +10011,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>437631</t>
+          <t>469180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>422922</t>
+          <t>455630</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>450185</t>
+          <t>483525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10046,32 +10046,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>872154</t>
+          <t>913019</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>846888</t>
+          <t>881743</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>896981</t>
+          <t>936385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -10089,32 +10089,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26691</t>
+          <t>28141</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44170</t>
+          <t>45491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>31365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10159,22 +10159,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47483</t>
+          <t>48747</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>36104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>67747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -10202,17 +10202,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10237,17 +10237,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10272,17 +10272,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10319,32 +10319,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10354,32 +10354,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10389,32 +10389,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -10432,32 +10432,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>227554</t>
+          <t>223622</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210731</t>
+          <t>206637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242573</t>
+          <t>239014</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10467,32 +10467,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>255048</t>
+          <t>259747</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>241345</t>
+          <t>242850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>270284</t>
+          <t>272403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10502,32 +10502,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>482601</t>
+          <t>483369</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>459453</t>
+          <t>460899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>502680</t>
+          <t>502478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -10545,32 +10545,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>76205</t>
+          <t>77332</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62337</t>
+          <t>63442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93312</t>
+          <t>93048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10580,32 +10580,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86340</t>
+          <t>86593</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71667</t>
+          <t>73469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100793</t>
+          <t>102436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10615,32 +10615,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>162545</t>
+          <t>163925</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143068</t>
+          <t>144903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182977</t>
+          <t>186237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -10658,17 +10658,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>315031</t>
+          <t>314908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>315031</t>
+          <t>314908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>315031</t>
+          <t>314908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10693,17 +10693,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10728,17 +10728,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>664158</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>664158</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>664158</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10775,32 +10775,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>31175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10810,32 +10810,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>241992</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99919</t>
+          <t>38243</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29481</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>285142</t>
+          <t>56156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -10888,32 +10888,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>120098</t>
+          <t>158463</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100450</t>
+          <t>135147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143024</t>
+          <t>186083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10923,32 +10923,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>210993</t>
+          <t>204872</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133162</t>
+          <t>184831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>266890</t>
+          <t>223967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10958,32 +10958,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>331091</t>
+          <t>363335</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248568</t>
+          <t>332322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391795</t>
+          <t>396172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -11001,32 +11001,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>180788</t>
+          <t>198902</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>158256</t>
+          <t>172211</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201741</t>
+          <t>224861</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11036,32 +11036,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>176476</t>
+          <t>194626</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>111583</t>
+          <t>177599</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>225771</t>
+          <t>215447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11071,32 +11071,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>357264</t>
+          <t>393529</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>257949</t>
+          <t>360992</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>409791</t>
+          <t>423525</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -11114,17 +11114,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11149,17 +11149,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11184,17 +11184,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11231,32 +11231,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>880</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -11276,12 +11276,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11301,32 +11301,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -11344,32 +11344,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>177069</t>
+          <t>201994</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>173899</t>
+          <t>196963</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>178417</t>
+          <t>204480</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11379,32 +11379,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>251761</t>
+          <t>222584</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>245537</t>
+          <t>219027</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>255585</t>
+          <t>225477</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11414,32 +11414,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>428829</t>
+          <t>424577</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>422142</t>
+          <t>418825</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>432886</t>
+          <t>428519</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>728</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11492,32 +11492,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11527,32 +11527,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -11570,17 +11570,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11640,17 +11640,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11687,32 +11687,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11550</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11722,17 +11722,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11757,32 +11757,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18090</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -11800,32 +11800,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>147105</t>
+          <t>152390</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131748</t>
+          <t>138784</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>161225</t>
+          <t>167941</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11835,32 +11835,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>137235</t>
+          <t>143110</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>124588</t>
+          <t>129132</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150808</t>
+          <t>155907</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11870,32 +11870,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>284340</t>
+          <t>295500</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>263155</t>
+          <t>276408</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>303499</t>
+          <t>314785</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>58,9%</t>
         </is>
       </c>
     </row>
@@ -11913,32 +11913,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>117389</t>
+          <t>112727</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102909</t>
+          <t>98620</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133626</t>
+          <t>126644</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11948,32 +11948,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>114481</t>
+          <t>115152</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100995</t>
+          <t>102802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>127399</t>
+          <t>128614</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11983,32 +11983,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>231869</t>
+          <t>227879</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>213275</t>
+          <t>208463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253175</t>
+          <t>247105</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -12026,17 +12026,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12061,17 +12061,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12096,17 +12096,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12143,32 +12143,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>201542</t>
+          <t>240246</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>175241</t>
+          <t>212190</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>228634</t>
+          <t>270606</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12178,32 +12178,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>214879</t>
+          <t>267239</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>107493</t>
+          <t>243154</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>291296</t>
+          <t>294738</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12213,32 +12213,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>416421</t>
+          <t>507485</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>268562</t>
+          <t>469558</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>498272</t>
+          <t>546492</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -12256,32 +12256,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>200272</t>
+          <t>221548</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>174467</t>
+          <t>194971</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>231385</t>
+          <t>253469</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12291,32 +12291,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>397404</t>
+          <t>231934</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>242686</t>
+          <t>208512</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>626924</t>
+          <t>257047</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12326,32 +12326,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>597676</t>
+          <t>453482</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>444491</t>
+          <t>415188</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>905663</t>
+          <t>493115</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -12369,32 +12369,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>222465</t>
+          <t>257893</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>194609</t>
+          <t>227530</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>249713</t>
+          <t>287549</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12404,32 +12404,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>236982</t>
+          <t>272884</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>111645</t>
+          <t>248556</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>322401</t>
+          <t>296606</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12439,32 +12439,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>459447</t>
+          <t>530777</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>294514</t>
+          <t>492282</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>547133</t>
+          <t>569066</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -12482,17 +12482,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12517,17 +12517,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12552,17 +12552,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12599,32 +12599,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12634,32 +12634,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27242</t>
+          <t>36987</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12669,32 +12669,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>34300</t>
+          <t>43737</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21303</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>49470</t>
+          <t>58717</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -12712,32 +12712,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>620784</t>
+          <t>725830</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>274083</t>
+          <t>708071</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>848763</t>
+          <t>743395</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12747,32 +12747,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>650111</t>
+          <t>747815</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>636660</t>
+          <t>731826</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>662432</t>
+          <t>762511</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12782,32 +12782,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1270896</t>
+          <t>1473645</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>792469</t>
+          <t>1447851</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1499292</t>
+          <t>1497609</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -12825,32 +12825,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>291123</t>
+          <t>53523</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>56879</t>
+          <t>39297</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>645064</t>
+          <t>70189</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12860,32 +12860,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>50133</t>
+          <t>58499</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>39139</t>
+          <t>46063</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>62232</t>
+          <t>70914</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12895,32 +12895,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>341256</t>
+          <t>112022</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>107403</t>
+          <t>92333</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>826550</t>
+          <t>132304</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -12938,17 +12938,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12973,17 +12973,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13008,17 +13008,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13055,32 +13055,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>276593</t>
+          <t>392665</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>411854</t>
+          <t>481883</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13090,32 +13090,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>443825</t>
+          <t>456129</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>358228</t>
+          <t>418692</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>630368</t>
+          <t>492341</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13125,32 +13125,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>805297</t>
+          <t>890406</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>697165</t>
+          <t>832728</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1008827</t>
+          <t>947016</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -13168,32 +13168,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2058920</t>
+          <t>2252433</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1564751</t>
+          <t>2188561</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2234341</t>
+          <t>2316488</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13203,32 +13203,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2477662</t>
+          <t>2423199</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2339506</t>
+          <t>2372164</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2684967</t>
+          <t>2475473</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13238,32 +13238,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4536582</t>
+          <t>4675633</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4000677</t>
+          <t>4579598</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4785092</t>
+          <t>4749899</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -13281,32 +13281,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1038405</t>
+          <t>844965</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>836418</t>
+          <t>790926</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1618815</t>
+          <t>905445</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13316,32 +13316,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>790793</t>
+          <t>857626</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>629149</t>
+          <t>813957</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>861343</t>
+          <t>901540</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13351,32 +13351,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1829198</t>
+          <t>1702592</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1589681</t>
+          <t>1631223</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2486275</t>
+          <t>1779453</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -13394,17 +13394,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3458797</t>
+          <t>3531676</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3458797</t>
+          <t>3531676</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3458797</t>
+          <t>3531676</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13429,17 +13429,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13464,17 +13464,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7171077</t>
+          <t>7268631</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7171077</t>
+          <t>7268631</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7171077</t>
+          <t>7268631</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
